--- a/Design files/Left-Side/BOM/eSpark BOM-LEFT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Left-Side/BOM/eSpark BOM-LEFT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
   <si>
     <t>Component list</t>
   </si>
@@ -60,15 +60,9 @@
     <t>Ferrite Bead</t>
   </si>
   <si>
-    <t>Test Point</t>
-  </si>
-  <si>
     <t>USB B Connector</t>
   </si>
   <si>
-    <t>SMD Pads</t>
-  </si>
-  <si>
     <t>Inductor</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Variable Resistor</t>
   </si>
   <si>
-    <t>Solder Bridge</t>
-  </si>
-  <si>
     <t>Switch</t>
   </si>
   <si>
@@ -123,18 +114,9 @@
     <t>FB1, FB2</t>
   </si>
   <si>
-    <t>J1, J4</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
@@ -147,9 +129,6 @@
     <t>LED2</t>
   </si>
   <si>
-    <t>P1, P2, P3</t>
-  </si>
-  <si>
     <t>R1, R6</t>
   </si>
   <si>
@@ -165,9 +144,6 @@
     <t>R12</t>
   </si>
   <si>
-    <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SB12, SB13, SB14</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -213,15 +189,9 @@
     <t>FERRITE BEAD 220 OHM 0603 1LN</t>
   </si>
   <si>
-    <t>Wire Connecting Pad</t>
-  </si>
-  <si>
     <t>CONN RCPT USB2.0 MICRO B SMD R/A</t>
   </si>
   <si>
-    <t>Wire Connecting Pads</t>
-  </si>
-  <si>
     <t>FIXED IND 2.7NH 500MA 200MOHM SM</t>
   </si>
   <si>
@@ -234,9 +204,6 @@
     <t>RED LED 0603 Light Emitting Diodes</t>
   </si>
   <si>
-    <t>Test Point ON</t>
-  </si>
-  <si>
     <t>RES 1K OHM 1% 1/20W 0201</t>
   </si>
   <si>
@@ -252,9 +219,6 @@
     <t>TRIMMER 1M OHM 0.1W J LEAD TOP</t>
   </si>
   <si>
-    <t>Solder Bridge ON</t>
-  </si>
-  <si>
     <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
   </si>
   <si>
@@ -291,30 +255,18 @@
     <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>2 Test Pad</t>
-  </si>
-  <si>
-    <t>5 Test Pad</t>
-  </si>
-  <si>
     <t>IND-0201</t>
   </si>
   <si>
     <t>LED-0603</t>
   </si>
   <si>
-    <t>Test-point - 0.5mm</t>
-  </si>
-  <si>
     <t>Res-0201</t>
   </si>
   <si>
     <t>TC33X-2-105E</t>
   </si>
   <si>
-    <t>Solder Bridge 0402</t>
-  </si>
-  <si>
     <t>B3U-1000P</t>
   </si>
   <si>
@@ -360,9 +312,6 @@
     <t>10118194-0001LF</t>
   </si>
   <si>
-    <t>4 Pin SMD Wire Connector</t>
-  </si>
-  <si>
     <t>LQP03TN2N7B02D</t>
   </si>
   <si>
@@ -606,7 +555,7 @@
     <t>Chipsmall</t>
   </si>
   <si>
-    <t>Custom Supplier Quote Required</t>
+    <t>Digikey</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1247,6 +1196,30 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1278,39 +1251,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1654,7 +1594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1688,15 +1628,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="69"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1707,7 +1647,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1732,7 +1672,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1746,7 +1686,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="70"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1757,7 +1697,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1771,7 +1711,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="71"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1796,7 +1736,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1817,7 +1757,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="71"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1838,7 +1778,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="71"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1859,7 +1799,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="71"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1870,52 +1810,52 @@
         <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -1928,28 +1868,28 @@
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G10" s="71" t="s">
-        <v>84</v>
+        <v>161</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>72</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="K10" s="71" t="s">
-        <v>179</v>
+        <v>162</v>
+      </c>
+      <c r="K10" s="61" t="s">
+        <v>162</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -1961,8 +1901,8 @@
       <c r="N10" s="37">
         <v>6</v>
       </c>
-      <c r="O10" s="73" t="s">
-        <v>194</v>
+      <c r="O10" s="63" t="s">
+        <v>177</v>
       </c>
       <c r="P10" s="38">
         <v>0.36</v>
@@ -1977,35 +1917,35 @@
     <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B32" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>104</v>
+        <v>73</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>88</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="K11" s="72" t="s">
-        <v>157</v>
+        <v>174</v>
+      </c>
+      <c r="K11" s="62" t="s">
+        <v>140</v>
       </c>
       <c r="L11" s="51">
         <v>18</v>
@@ -2017,8 +1957,8 @@
       <c r="N11" s="51">
         <v>100</v>
       </c>
-      <c r="O11" s="73" t="s">
-        <v>188</v>
+      <c r="O11" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P11" s="52">
         <v>2.8E-3</v>
@@ -2040,28 +1980,28 @@
         <v>10</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="71" t="s">
-        <v>105</v>
+        <v>74</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>89</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J12" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" s="61" t="s">
         <v>141</v>
-      </c>
-      <c r="K12" s="71" t="s">
-        <v>158</v>
       </c>
       <c r="L12" s="37">
         <v>6</v>
@@ -2073,8 +2013,8 @@
       <c r="N12" s="37">
         <v>50</v>
       </c>
-      <c r="O12" s="73" t="s">
-        <v>188</v>
+      <c r="O12" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P12" s="38">
         <v>9.7999999999999997E-3</v>
@@ -2096,28 +2036,28 @@
         <v>10</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="72" t="s">
-        <v>106</v>
+        <v>75</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>90</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J13" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="62" t="s">
         <v>142</v>
-      </c>
-      <c r="K13" s="72" t="s">
-        <v>159</v>
       </c>
       <c r="L13" s="51">
         <v>4</v>
@@ -2129,8 +2069,8 @@
       <c r="N13" s="51">
         <v>100</v>
       </c>
-      <c r="O13" s="73" t="s">
-        <v>188</v>
+      <c r="O13" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P13" s="52">
         <v>1.1999999999999999E-3</v>
@@ -2152,28 +2092,28 @@
         <v>10</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="71" t="s">
-        <v>107</v>
+        <v>75</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>91</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J14" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="61" t="s">
         <v>143</v>
-      </c>
-      <c r="K14" s="71" t="s">
-        <v>160</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2185,8 +2125,8 @@
       <c r="N14" s="37">
         <v>100</v>
       </c>
-      <c r="O14" s="73" t="s">
-        <v>188</v>
+      <c r="O14" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P14" s="38">
         <v>4.3E-3</v>
@@ -2208,28 +2148,28 @@
         <v>10</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="72" t="s">
-        <v>108</v>
+        <v>75</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>92</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J15" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="62" t="s">
         <v>144</v>
-      </c>
-      <c r="K15" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -2241,8 +2181,8 @@
       <c r="N15" s="51">
         <v>100</v>
       </c>
-      <c r="O15" s="73" t="s">
-        <v>188</v>
+      <c r="O15" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P15" s="52">
         <v>4.4000000000000003E-3</v>
@@ -2264,28 +2204,28 @@
         <v>10</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="71" t="s">
-        <v>109</v>
+        <v>75</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>93</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J16" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" s="61" t="s">
         <v>145</v>
-      </c>
-      <c r="K16" s="71" t="s">
-        <v>162</v>
       </c>
       <c r="L16" s="37">
         <v>2</v>
@@ -2297,8 +2237,8 @@
       <c r="N16" s="37">
         <v>100</v>
       </c>
-      <c r="O16" s="73" t="s">
-        <v>188</v>
+      <c r="O16" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P16" s="38">
         <v>4.3E-3</v>
@@ -2320,28 +2260,28 @@
         <v>11</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>110</v>
+        <v>76</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>94</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="K17" s="72" t="s">
-        <v>179</v>
+        <v>129</v>
+      </c>
+      <c r="K17" s="62" t="s">
+        <v>162</v>
       </c>
       <c r="L17" s="51">
         <v>4</v>
@@ -2353,8 +2293,8 @@
       <c r="N17" s="51">
         <v>40</v>
       </c>
-      <c r="O17" s="73" t="s">
-        <v>188</v>
+      <c r="O17" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P17" s="52">
         <v>3.1199999999999999E-2</v>
@@ -2376,28 +2316,28 @@
         <v>12</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="71" t="s">
-        <v>111</v>
+        <v>77</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>95</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="K18" s="72" t="s">
-        <v>179</v>
+        <v>130</v>
+      </c>
+      <c r="K18" s="62" t="s">
+        <v>162</v>
       </c>
       <c r="L18" s="37">
         <v>2</v>
@@ -2409,8 +2349,8 @@
       <c r="N18" s="37">
         <v>50</v>
       </c>
-      <c r="O18" s="73" t="s">
-        <v>188</v>
+      <c r="O18" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P18" s="38">
         <v>1.8800000000000001E-2</v>
@@ -2424,277 +2364,280 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="47">
-        <f t="shared" si="0"/>
+      <c r="B19" s="46">
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G19" s="75" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="I19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="J19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="K19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="L19" s="75">
-        <v>2</v>
-      </c>
-      <c r="M19" s="74">
-        <f t="shared" ref="M19" si="9">L19*5</f>
+      <c r="D19" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="K19" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="L19" s="37">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f>L19*5</f>
+        <v>5</v>
+      </c>
+      <c r="N19" s="37">
         <v>10</v>
       </c>
-      <c r="N19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="O19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="P19" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q19" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="R19" s="74"/>
-      <c r="S19" s="74"/>
+      <c r="O19" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P19" s="38">
+        <v>0.19270000000000001</v>
+      </c>
+      <c r="Q19" s="38">
+        <f>P19*N19</f>
+        <v>1.927</v>
+      </c>
+      <c r="R19" s="37"/>
+      <c r="S19" s="59"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="46">
-        <f>ROW(B20) - ROW($B$9)</f>
+      <c r="B20" s="47">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G20" s="71" t="s">
-        <v>112</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="K20" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L20" s="37">
+      <c r="D20" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="K20" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="L20" s="51">
         <v>1</v>
       </c>
-      <c r="M20" s="37">
-        <f>L20*5</f>
+      <c r="M20" s="51">
+        <f t="shared" ref="M20" si="9">L20*5</f>
         <v>5</v>
       </c>
-      <c r="N20" s="37">
-        <v>10</v>
-      </c>
-      <c r="O20" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P20" s="38">
-        <v>0.19270000000000001</v>
-      </c>
-      <c r="Q20" s="38">
-        <f>P20*N20</f>
-        <v>1.927</v>
-      </c>
-      <c r="R20" s="37"/>
+      <c r="N20" s="51">
+        <v>100</v>
+      </c>
+      <c r="O20" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P20" s="52">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="Q20" s="52">
+        <f t="shared" ref="Q20" si="10">P20*N20</f>
+        <v>0.44</v>
+      </c>
+      <c r="R20" s="51"/>
       <c r="S20" s="59"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="47">
+      <c r="B21" s="46">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="L21" s="37">
+        <v>2</v>
+      </c>
+      <c r="M21" s="37">
+        <f>L21*5</f>
+        <v>10</v>
+      </c>
+      <c r="N21" s="37">
+        <v>100</v>
+      </c>
+      <c r="O21" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P21" s="38">
+        <v>4.7199999999999999E-2</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>P21*N21</f>
+        <v>4.72</v>
+      </c>
+      <c r="R21" s="37"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="47">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G21" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="I21" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="J21" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="K21" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="L21" s="74">
+      <c r="C22" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="J22" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="K22" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="L22" s="51">
         <v>1</v>
       </c>
-      <c r="M21" s="74">
-        <f t="shared" ref="M21" si="10">L21*5</f>
+      <c r="M22" s="51">
+        <f t="shared" ref="M22" si="11">L22*5</f>
         <v>5</v>
       </c>
-      <c r="N21" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="O21" s="76" t="s">
-        <v>179</v>
-      </c>
-      <c r="P21" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q21" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="R21" s="74"/>
-      <c r="S21" s="78"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="46">
-        <f>ROW(B22) - ROW($B$9)</f>
-        <v>13</v>
-      </c>
-      <c r="C22" s="53" t="s">
+      <c r="N22" s="51">
+        <v>20</v>
+      </c>
+      <c r="O22" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P22" s="52">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="Q22" s="52">
+        <f t="shared" ref="Q22" si="12">P22*N22</f>
+        <v>0.626</v>
+      </c>
+      <c r="R22" s="51"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="46">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="74" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G22" s="75" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="J22" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="K22" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="L22" s="74">
+      <c r="D23" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="L23" s="37">
         <v>1</v>
       </c>
-      <c r="M22" s="74">
-        <f>L22*5</f>
+      <c r="M23" s="37">
+        <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="O22" s="76" t="s">
-        <v>179</v>
-      </c>
-      <c r="P22" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q22" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="R22" s="74"/>
-      <c r="S22" s="78"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="47">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="K23" s="72" t="s">
-        <v>163</v>
-      </c>
-      <c r="L23" s="51">
-        <v>1</v>
-      </c>
-      <c r="M23" s="51">
-        <f t="shared" ref="M23" si="11">L23*5</f>
-        <v>5</v>
-      </c>
-      <c r="N23" s="51">
-        <v>100</v>
-      </c>
-      <c r="O23" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P23" s="52">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="Q23" s="52">
-        <f t="shared" ref="Q23" si="12">P23*N23</f>
-        <v>0.44</v>
-      </c>
-      <c r="R23" s="51"/>
+      <c r="N23" s="37">
+        <v>20</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P23" s="38">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2703,32 +2646,32 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="54" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="71" t="s">
-        <v>115</v>
+        <v>80</v>
+      </c>
+      <c r="G24" s="66" t="s">
+        <v>101</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J24" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="K24" s="61" t="s">
         <v>150</v>
-      </c>
-      <c r="K24" s="71" t="s">
-        <v>164</v>
       </c>
       <c r="L24" s="37">
         <v>2</v>
@@ -2740,127 +2683,127 @@
       <c r="N24" s="37">
         <v>100</v>
       </c>
-      <c r="O24" s="73" t="s">
-        <v>188</v>
+      <c r="O24" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P24" s="38">
-        <v>4.7199999999999999E-2</v>
+        <v>1.9E-3</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>4.72</v>
+        <v>0.19</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="47">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="72" t="s">
-        <v>116</v>
+        <v>80</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>102</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J25" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="K25" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="K25" s="72" t="s">
-        <v>165</v>
-      </c>
       <c r="L25" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="51">
         <f t="shared" ref="M25" si="13">L25*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N25" s="51">
-        <v>20</v>
-      </c>
-      <c r="O25" s="73" t="s">
-        <v>188</v>
+        <v>100</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P25" s="52">
-        <v>3.1300000000000001E-2</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="14">P25*N25</f>
-        <v>0.626</v>
+        <v>0.09</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="46">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="71" t="s">
-        <v>117</v>
+        <v>80</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>103</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J26" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="K26" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="K26" s="71" t="s">
-        <v>166</v>
-      </c>
       <c r="L26" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26" s="37">
         <f>L26*5</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N26" s="37">
-        <v>20</v>
-      </c>
-      <c r="O26" s="73" t="s">
-        <v>188</v>
+        <v>100</v>
+      </c>
+      <c r="O26" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="P26" s="38">
-        <v>2.0799999999999999E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>0.41599999999999998</v>
+        <v>0.1</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
@@ -2872,53 +2815,54 @@
         <v>18</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G27" s="75" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="J27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="K27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="L27" s="75">
-        <v>3</v>
-      </c>
-      <c r="M27" s="74">
+        <v>16</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="L27" s="51">
+        <v>6</v>
+      </c>
+      <c r="M27" s="51">
         <f t="shared" ref="M27" si="15">L27*5</f>
-        <v>15</v>
-      </c>
-      <c r="N27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="O27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="P27" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q27" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="R27" s="74"/>
-      <c r="S27" s="74"/>
+        <v>30</v>
+      </c>
+      <c r="N27" s="51">
+        <v>100</v>
+      </c>
+      <c r="O27" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P27" s="52">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q27" s="52">
+        <f t="shared" ref="Q27" si="16">P27*N27</f>
+        <v>0.09</v>
+      </c>
+      <c r="R27" s="51"/>
+      <c r="S27" s="59"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -2926,718 +2870,447 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="54" t="s">
-        <v>18</v>
+      <c r="C28" s="53" t="s">
+        <v>17</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="H28" s="37" t="s">
-        <v>128</v>
-      </c>
       <c r="I28" s="37" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="K28" s="71" t="s">
-        <v>167</v>
+        <v>162</v>
+      </c>
+      <c r="K28" s="61" t="s">
+        <v>154</v>
       </c>
       <c r="L28" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="37">
         <f>L28*5</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N28" s="37">
-        <v>100</v>
-      </c>
-      <c r="O28" s="73" t="s">
-        <v>188</v>
+        <v>6</v>
+      </c>
+      <c r="O28" s="63" t="s">
+        <v>177</v>
       </c>
       <c r="P28" s="38">
-        <v>1.9E-3</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.19</v>
+        <v>1.7639999999999998</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="47">
-        <f t="shared" si="0"/>
+      <c r="B29" s="46">
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="G29" s="72" t="s">
+      <c r="D29" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="H29" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="I29" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="J29" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="K29" s="72" t="s">
-        <v>168</v>
-      </c>
-      <c r="L29" s="51">
-        <v>2</v>
-      </c>
-      <c r="M29" s="51">
-        <f t="shared" ref="M29" si="16">L29*5</f>
-        <v>10</v>
-      </c>
-      <c r="N29" s="51">
-        <v>100</v>
-      </c>
-      <c r="O29" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P29" s="52">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="17">P29*N29</f>
-        <v>0.09</v>
-      </c>
-      <c r="R29" s="51"/>
+      <c r="I29" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K29" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="L29" s="37">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f>L29*5</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="37">
+        <v>6</v>
+      </c>
+      <c r="O29" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="P29" s="38">
+        <v>0.92730999999999997</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>5.56386</v>
+      </c>
+      <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="46">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="47">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="G30" s="71" t="s">
+      <c r="C30" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="H30" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="K30" s="71" t="s">
-        <v>169</v>
-      </c>
-      <c r="L30" s="37">
-        <v>3</v>
-      </c>
-      <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>15</v>
-      </c>
-      <c r="N30" s="37">
-        <v>100</v>
-      </c>
-      <c r="O30" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P30" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q30" s="38">
-        <f>P30*N30</f>
-        <v>0.1</v>
-      </c>
-      <c r="R30" s="37"/>
+      <c r="I30" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="K30" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="L30" s="51">
+        <v>1</v>
+      </c>
+      <c r="M30" s="51">
+        <f t="shared" ref="M30" si="17">L30*5</f>
+        <v>5</v>
+      </c>
+      <c r="N30" s="51">
+        <v>6</v>
+      </c>
+      <c r="O30" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="P30" s="52">
+        <v>13.868</v>
+      </c>
+      <c r="Q30" s="52">
+        <f t="shared" ref="Q30" si="18">P30*N30</f>
+        <v>83.207999999999998</v>
+      </c>
+      <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="47">
-        <f t="shared" si="0"/>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="G31" s="72" t="s">
+      <c r="C31" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="H31" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="I31" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="J31" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="K31" s="72" t="s">
-        <v>170</v>
-      </c>
-      <c r="L31" s="51">
-        <v>6</v>
-      </c>
-      <c r="M31" s="51">
-        <f t="shared" ref="M31" si="18">L31*5</f>
-        <v>30</v>
-      </c>
-      <c r="N31" s="51">
-        <v>100</v>
-      </c>
-      <c r="O31" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P31" s="52">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="19">P31*N31</f>
-        <v>0.09</v>
-      </c>
-      <c r="R31" s="51"/>
+      <c r="I31" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="K31" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="L31" s="37">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f>L31*5</f>
+        <v>5</v>
+      </c>
+      <c r="N31" s="37">
+        <v>10</v>
+      </c>
+      <c r="O31" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P31" s="38">
+        <v>0.32479999999999998</v>
+      </c>
+      <c r="Q31" s="38">
+        <f>P31*N31</f>
+        <v>3.2479999999999998</v>
+      </c>
+      <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="47">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" s="37" t="s">
+      <c r="D32" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="I32" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="J32" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="K32" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="L32" s="51">
+        <v>1</v>
+      </c>
+      <c r="M32" s="51">
+        <f t="shared" ref="M32" si="19">L32*5</f>
+        <v>5</v>
+      </c>
+      <c r="N32" s="51">
+        <v>6</v>
+      </c>
+      <c r="O32" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="K32" s="71" t="s">
-        <v>171</v>
-      </c>
-      <c r="L32" s="37">
+      <c r="P32" s="52">
         <v>1</v>
       </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="37">
+      <c r="Q32" s="52">
+        <f t="shared" ref="Q32" si="20">P32*N32</f>
         <v>6</v>
       </c>
-      <c r="O32" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="P32" s="38">
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="Q32" s="38">
-        <f>P32*N32</f>
-        <v>1.7639999999999998</v>
-      </c>
-      <c r="R32" s="37"/>
-      <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="R32" s="51"/>
+      <c r="S32" s="67"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47">
-        <f t="shared" si="0"/>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" s="74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="75" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="I33" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="J33" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="K33" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="L33" s="74">
-        <v>14</v>
-      </c>
-      <c r="M33" s="74">
-        <f t="shared" ref="M33" si="20">L33*5</f>
+      <c r="D33" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="N33" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="O33" s="76" t="s">
-        <v>179</v>
-      </c>
-      <c r="P33" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q33" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="R33" s="74"/>
-      <c r="S33" s="78"/>
+      <c r="F33" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="G33" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="K33" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f>L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="37">
+        <v>10</v>
+      </c>
+      <c r="O33" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.24129999999999999</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>2.4129999999999998</v>
+      </c>
+      <c r="R33" s="37"/>
+      <c r="S33" s="65"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
+        <f t="shared" ref="B34:B35" si="21">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G34" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="K34" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L34" s="37">
-        <v>1</v>
-      </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
-        <v>5</v>
-      </c>
-      <c r="N34" s="37">
-        <v>6</v>
-      </c>
-      <c r="O34" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="P34" s="38">
-        <v>0.92730999999999997</v>
-      </c>
-      <c r="Q34" s="38">
-        <f>P34*N34</f>
-        <v>5.56386</v>
-      </c>
+      <c r="C34" s="54" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="47">
-        <f t="shared" si="0"/>
+      <c r="B35" s="46">
+        <f t="shared" si="21"/>
         <v>26</v>
       </c>
-      <c r="C35" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="G35" s="72" t="s">
-        <v>122</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="J35" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="K35" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L35" s="51">
-        <v>1</v>
-      </c>
-      <c r="M35" s="51">
-        <f t="shared" ref="M35" si="21">L35*5</f>
+      <c r="C35" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
+      <c r="N35" s="37"/>
+      <c r="O35" s="37"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="39"/>
+    </row>
+    <row r="36" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="N35" s="51">
+      <c r="O36" s="77"/>
+      <c r="P36" s="77"/>
+      <c r="Q36" s="48">
+        <f>SUM(Q10:Q35)</f>
+        <v>117.33386</v>
+      </c>
+      <c r="R36" s="72"/>
+      <c r="S36" s="73"/>
+    </row>
+    <row r="37" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="O35" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="P35" s="52">
-        <v>13.868</v>
-      </c>
-      <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="22">P35*N35</f>
-        <v>83.207999999999998</v>
-      </c>
-      <c r="R35" s="51"/>
-      <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="46">
-        <f>ROW(B36) - ROW($B$9)</f>
-        <v>27</v>
-      </c>
-      <c r="C36" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="G36" s="71" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="K36" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L36" s="37">
-        <v>1</v>
-      </c>
-      <c r="M36" s="37">
-        <f>L36*5</f>
-        <v>5</v>
-      </c>
-      <c r="N36" s="37">
-        <v>10</v>
-      </c>
-      <c r="O36" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P36" s="38">
-        <v>0.32479999999999998</v>
-      </c>
-      <c r="Q36" s="38">
-        <f>P36*N36</f>
-        <v>3.2479999999999998</v>
-      </c>
-      <c r="R36" s="37"/>
-      <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="47">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="G37" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H37" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L37" s="51">
-        <v>1</v>
-      </c>
-      <c r="M37" s="51">
-        <f t="shared" ref="M37" si="23">L37*5</f>
-        <v>5</v>
-      </c>
-      <c r="N37" s="51"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="52"/>
-      <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="24">P37*N37</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="51"/>
-      <c r="S37" s="80" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="46">
-        <f>ROW(B38) - ROW($B$9)</f>
-        <v>29</v>
-      </c>
-      <c r="C38" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="F38" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G38" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="H38" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="K38" s="72" t="s">
-        <v>172</v>
-      </c>
-      <c r="L38" s="37">
-        <v>1</v>
-      </c>
-      <c r="M38" s="37">
-        <f>L38*5</f>
-        <v>5</v>
-      </c>
-      <c r="N38" s="37">
-        <v>10</v>
-      </c>
-      <c r="O38" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="P38" s="38">
-        <v>0.24129999999999999</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>2.4129999999999998</v>
-      </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="78"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="46">
-        <f t="shared" ref="B39:B40" si="25">ROW(B39) - ROW($B$9)</f>
-        <v>30</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="37"/>
-      <c r="L39" s="37"/>
-      <c r="M39" s="37"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="37"/>
-      <c r="P39" s="38"/>
-      <c r="Q39" s="38"/>
-      <c r="R39" s="37"/>
-      <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="46">
-        <f t="shared" si="25"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="70" t="s">
-        <v>177</v>
-      </c>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="37"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="38"/>
-      <c r="Q40" s="38"/>
-      <c r="R40" s="37"/>
-      <c r="S40" s="39"/>
-    </row>
-    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="48">
-        <f>SUM(Q10:Q40)</f>
-        <v>111.33386</v>
-      </c>
-      <c r="R41" s="64"/>
-      <c r="S41" s="65"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="O42" s="69"/>
-      <c r="P42" s="69"/>
-      <c r="Q42" s="49">
-        <f>Q41/5</f>
-        <v>22.266772</v>
-      </c>
-      <c r="R42" s="66"/>
-      <c r="S42" s="67"/>
+      <c r="O37" s="77"/>
+      <c r="P37" s="77"/>
+      <c r="Q37" s="49">
+        <f>Q36/5</f>
+        <v>23.466771999999999</v>
+      </c>
+      <c r="R37" s="74"/>
+      <c r="S37" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R41:S42"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R36:S37"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O12" r:id="rId1"/>
@@ -3647,25 +3320,26 @@
     <hyperlink ref="O16" r:id="rId5"/>
     <hyperlink ref="O17" r:id="rId6"/>
     <hyperlink ref="O18" r:id="rId7"/>
-    <hyperlink ref="O20" r:id="rId8"/>
-    <hyperlink ref="O23" r:id="rId9"/>
-    <hyperlink ref="O24" r:id="rId10"/>
-    <hyperlink ref="O25" r:id="rId11"/>
-    <hyperlink ref="O26" r:id="rId12"/>
-    <hyperlink ref="O29" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O31" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O27" r:id="rId15"/>
+    <hyperlink ref="O31" r:id="rId16"/>
+    <hyperlink ref="O33" r:id="rId17"/>
     <hyperlink ref="O11" r:id="rId18"/>
-    <hyperlink ref="O28" r:id="rId19"/>
+    <hyperlink ref="O24" r:id="rId19"/>
     <hyperlink ref="O10" r:id="rId20"/>
-    <hyperlink ref="O32" r:id="rId21"/>
-    <hyperlink ref="O34" r:id="rId22"/>
-    <hyperlink ref="O35" r:id="rId23"/>
+    <hyperlink ref="O28" r:id="rId21"/>
+    <hyperlink ref="O29" r:id="rId22"/>
+    <hyperlink ref="O30" r:id="rId23"/>
+    <hyperlink ref="O32" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
-  <drawing r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <drawing r:id="rId26"/>
 </worksheet>
 </file>
--- a/Design files/Left-Side/BOM/eSpark BOM-LEFT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Left-Side/BOM/eSpark BOM-LEFT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="184">
   <si>
     <t>Component list</t>
   </si>
@@ -556,6 +556,21 @@
   </si>
   <si>
     <t>Digikey</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>3.7V Lithium Polymer Rechargeable Battery 501230 300mah</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Bone Conduction Module Sensor Deafness Dumb Mini bone conduction horn speaker (GD02)</t>
+  </si>
+  <si>
+    <t>Transducer (GD02)</t>
   </si>
 </sst>
 </file>
@@ -1615,6 +1630,9 @@
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3200,7 +3218,7 @@
       <c r="R33" s="37"/>
       <c r="S33" s="65"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="46">
         <f t="shared" ref="B34:B35" si="21">ROW(B34) - ROW($B$9)</f>
@@ -3209,24 +3227,54 @@
       <c r="C34" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
+      <c r="D34" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f>L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="37">
+        <v>10</v>
+      </c>
+      <c r="O34" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.97</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>9.6999999999999993</v>
+      </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="46">
         <f t="shared" si="21"/>
@@ -3235,20 +3283,50 @@
       <c r="C35" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="38"/>
-      <c r="Q35" s="38"/>
+      <c r="D35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L35" s="37">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f>L35*5</f>
+        <v>5</v>
+      </c>
+      <c r="N35" s="37">
+        <v>6</v>
+      </c>
+      <c r="O35" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="P35" s="38">
+        <v>3.93</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>23.580000000000002</v>
+      </c>
       <c r="R35" s="37"/>
       <c r="S35" s="39"/>
     </row>
@@ -3273,7 +3351,7 @@
       <c r="P36" s="77"/>
       <c r="Q36" s="48">
         <f>SUM(Q10:Q35)</f>
-        <v>117.33386</v>
+        <v>150.61386000000002</v>
       </c>
       <c r="R36" s="72"/>
       <c r="S36" s="73"/>
@@ -3299,7 +3377,7 @@
       <c r="P37" s="77"/>
       <c r="Q37" s="49">
         <f>Q36/5</f>
-        <v>23.466771999999999</v>
+        <v>30.122772000000005</v>
       </c>
       <c r="R37" s="74"/>
       <c r="S37" s="75"/>
@@ -3337,9 +3415,11 @@
     <hyperlink ref="O29" r:id="rId22"/>
     <hyperlink ref="O30" r:id="rId23"/>
     <hyperlink ref="O32" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
-  <drawing r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>
--- a/Design files/Left-Side/BOM/eSpark BOM-LEFT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Left-Side/BOM/eSpark BOM-LEFT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="186">
   <si>
     <t>Component list</t>
   </si>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>Transducer (GD02)</t>
+  </si>
+  <si>
+    <t>Touch Material</t>
+  </si>
+  <si>
+    <t>TO be Confirmed By Mechanical Team</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -3221,7 +3227,7 @@
     <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="46">
-        <f t="shared" ref="B34:B35" si="21">ROW(B34) - ROW($B$9)</f>
+        <f t="shared" ref="B34:B36" si="21">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="54" t="s">
@@ -3274,121 +3280,167 @@
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="46">
         <f t="shared" si="21"/>
         <v>26</v>
       </c>
-      <c r="C35" s="60" t="s">
+      <c r="C35" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" s="37" t="s">
+      <c r="D35" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="37"/>
+      <c r="F35" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L35" s="51">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <v>5</v>
+      </c>
+      <c r="N35" s="37"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="67" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="46">
+        <f t="shared" si="21"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E36" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="F35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="G35" s="37" t="s">
+      <c r="F36" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="H35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="L35" s="37">
+      <c r="H36" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L36" s="37">
         <v>1</v>
       </c>
-      <c r="M35" s="37">
-        <f>L35*5</f>
+      <c r="M36" s="37">
+        <f>L36*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N36" s="37">
         <v>6</v>
       </c>
-      <c r="O35" s="63" t="s">
+      <c r="O36" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="P35" s="38">
+      <c r="P36" s="38">
         <v>3.93</v>
       </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
         <v>23.580000000000002</v>
       </c>
-      <c r="R35" s="37"/>
-      <c r="S35" s="39"/>
-    </row>
-    <row r="36" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="44"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="76" t="s">
-        <v>5</v>
-      </c>
-      <c r="O36" s="77"/>
-      <c r="P36" s="77"/>
-      <c r="Q36" s="48">
-        <f>SUM(Q10:Q35)</f>
-        <v>150.61386000000002</v>
-      </c>
-      <c r="R36" s="72"/>
-      <c r="S36" s="73"/>
+      <c r="R36" s="37"/>
+      <c r="S36" s="39"/>
     </row>
     <row r="37" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
       <c r="N37" s="76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37" s="77"/>
       <c r="P37" s="77"/>
-      <c r="Q37" s="49">
-        <f>Q36/5</f>
+      <c r="Q37" s="48">
+        <f>SUM(Q10:Q36)</f>
+        <v>150.61386000000002</v>
+      </c>
+      <c r="R37" s="72"/>
+      <c r="S37" s="73"/>
+    </row>
+    <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="76" t="s">
+        <v>6</v>
+      </c>
+      <c r="O38" s="77"/>
+      <c r="P38" s="77"/>
+      <c r="Q38" s="49">
+        <f>Q37/5</f>
         <v>30.122772000000005</v>
       </c>
-      <c r="R37" s="74"/>
-      <c r="S37" s="75"/>
+      <c r="R38" s="74"/>
+      <c r="S38" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R36:S37"/>
-    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R37:S38"/>
     <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N38:P38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O12" r:id="rId1"/>
@@ -3416,7 +3468,7 @@
     <hyperlink ref="O30" r:id="rId23"/>
     <hyperlink ref="O32" r:id="rId24"/>
     <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O36" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
